--- a/data/trans_orig/IQ27-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, referido por progenitor/a</t>
+          <t>Peso medio, en kilogramos, declarado por progenitor/a (tasa de respuesta: 96,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +716,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,8; 34,05</t>
+          <t>26,88; 34,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,76; 32,73</t>
+          <t>25,53; 32,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,94; 34,03</t>
+          <t>26,65; 33,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,12; 31,79</t>
+          <t>23,83; 32,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,81; 40,36</t>
+          <t>30,72; 39,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,61; 33,01</t>
+          <t>25,55; 32,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,9; 35,61</t>
+          <t>27,0; 36,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,52; 34,35</t>
+          <t>26,94; 34,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,98; 35,92</t>
+          <t>30,13; 36,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,58; 31,57</t>
+          <t>26,48; 31,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,88; 33,4</t>
+          <t>27,97; 33,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,51; 32,06</t>
+          <t>26,55; 32,13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +856,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,16; 33,53</t>
+          <t>28,06; 33,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,05; 31,55</t>
+          <t>26,44; 31,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,67; 34,37</t>
+          <t>28,51; 34,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,77; 49,8</t>
+          <t>34,41; 49,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,87; 38,76</t>
+          <t>33,1; 39,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,77; 31,99</t>
+          <t>27,03; 32,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,24; 34,47</t>
+          <t>29,38; 34,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,88; 43,29</t>
+          <t>34,16; 43,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,4; 35,37</t>
+          <t>31,31; 35,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,4; 31,09</t>
+          <t>27,4; 30,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,42; 33,3</t>
+          <t>29,6; 33,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,63; 46,4</t>
+          <t>35,5; 45,55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,48; 36,76</t>
+          <t>29,16; 35,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,74; 33,05</t>
+          <t>25,78; 32,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,76; 33,64</t>
+          <t>26,67; 33,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,09; 37,46</t>
+          <t>30,27; 37,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,31; 37,8</t>
+          <t>30,41; 38,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,24; 37,14</t>
+          <t>29,43; 37,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,01; 34,53</t>
+          <t>27,96; 34,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,8; 42,74</t>
+          <t>34,63; 42,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,76; 36,05</t>
+          <t>30,69; 35,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,75; 33,71</t>
+          <t>28,51; 33,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,24; 33,23</t>
+          <t>28,44; 33,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,36; 38,72</t>
+          <t>33,84; 39,0</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,37; 37,0</t>
+          <t>30,16; 37,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,61; 31,75</t>
+          <t>25,38; 31,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,54; 35,99</t>
+          <t>27,68; 35,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,95; 37,14</t>
+          <t>29,18; 37,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,18; 37,49</t>
+          <t>30,33; 37,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,03; 33,01</t>
+          <t>26,41; 33,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,3; 36,23</t>
+          <t>28,9; 36,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,28; 43,57</t>
+          <t>31,32; 43,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,23; 36,14</t>
+          <t>31,03; 36,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,77; 31,22</t>
+          <t>26,62; 30,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,54; 35,07</t>
+          <t>29,7; 34,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,66; 39,78</t>
+          <t>31,78; 39,68</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,83; 34,84</t>
+          <t>26,72; 34,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,99; 33,5</t>
+          <t>25,0; 33,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,29; 32,02</t>
+          <t>24,53; 31,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30,59; 39,05</t>
+          <t>30,14; 38,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,42; 38,07</t>
+          <t>29,77; 38,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,52; 38,51</t>
+          <t>28,28; 38,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,07; 36,21</t>
+          <t>27,88; 35,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,39; 48,97</t>
+          <t>37,6; 48,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,43; 35,21</t>
+          <t>29,56; 35,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,23; 34,85</t>
+          <t>28,1; 34,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,53; 32,95</t>
+          <t>27,42; 32,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,11; 42,07</t>
+          <t>35,12; 42,33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1416,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,91; 36,48</t>
+          <t>29,08; 36,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,85; 35,92</t>
+          <t>28,11; 36,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,76; 35,88</t>
+          <t>29,08; 36,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,5; 35,33</t>
+          <t>28,43; 35,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,55; 42,3</t>
+          <t>33,37; 41,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,06; 38,19</t>
+          <t>28,8; 38,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,65; 37,39</t>
+          <t>29,66; 37,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,75; 37,1</t>
+          <t>29,02; 37,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,27; 38,24</t>
+          <t>32,52; 38,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,93; 35,71</t>
+          <t>30,05; 36,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30,08; 35,46</t>
+          <t>30,21; 35,67</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,84; 35,32</t>
+          <t>29,88; 35,21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,75; 33,56</t>
+          <t>28,86; 33,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,33; 33,45</t>
+          <t>28,48; 33,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,58; 31,99</t>
+          <t>27,5; 32,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,15; 39,03</t>
+          <t>33,2; 39,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,81; 35,7</t>
+          <t>29,92; 35,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,59; 33,11</t>
+          <t>27,76; 32,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,91; 31,73</t>
+          <t>27,0; 31,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,28; 46,68</t>
+          <t>37,84; 45,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,94; 33,8</t>
+          <t>29,95; 33,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,47; 32,64</t>
+          <t>28,83; 32,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,87; 31,08</t>
+          <t>27,84; 31,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,62; 41,96</t>
+          <t>36,65; 42,09</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>29,73; 33,76</t>
+          <t>29,87; 34,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,04; 32,16</t>
+          <t>28,15; 32,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,9; 30,71</t>
+          <t>26,79; 30,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32,8; 37,21</t>
+          <t>33,08; 37,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,11; 34,63</t>
+          <t>30,18; 34,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,54; 32,7</t>
+          <t>28,74; 33,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,6; 31,89</t>
+          <t>27,68; 32,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,71; 40,97</t>
+          <t>35,28; 40,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,65; 33,65</t>
+          <t>30,68; 33,61</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28,93; 31,83</t>
+          <t>28,93; 31,8</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27,77; 30,78</t>
+          <t>27,85; 30,79</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,12; 38,62</t>
+          <t>34,98; 38,77</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30,58; 32,7</t>
+          <t>30,74; 32,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28,73; 30,91</t>
+          <t>28,72; 30,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,08; 31,15</t>
+          <t>29,07; 31,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33,43; 38,48</t>
+          <t>33,25; 39,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,79; 35,17</t>
+          <t>32,83; 35,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,52; 31,89</t>
+          <t>29,67; 32,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,86; 31,96</t>
+          <t>29,94; 32,09</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36,18; 39,47</t>
+          <t>36,38; 39,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32,09; 33,71</t>
+          <t>32,11; 33,67</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29,51; 31,15</t>
+          <t>29,54; 31,01</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29,8; 31,25</t>
+          <t>29,82; 31,29</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>35,29; 38,41</t>
+          <t>35,32; 38,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Provincia-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,88; 34,16</t>
+          <t>26,74; 34,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,53; 32,65</t>
+          <t>25,97; 33,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,65; 33,55</t>
+          <t>26,98; 33,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,83; 32,18</t>
+          <t>23,69; 31,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,72; 39,56</t>
+          <t>30,64; 40,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,55; 32,74</t>
+          <t>25,56; 32,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,0; 36,34</t>
+          <t>26,7; 35,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,94; 34,32</t>
+          <t>26,75; 34,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,13; 36,04</t>
+          <t>29,68; 35,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,48; 31,53</t>
+          <t>26,68; 31,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,97; 33,53</t>
+          <t>27,94; 33,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,55; 32,13</t>
+          <t>26,23; 31,92</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,06; 33,21</t>
+          <t>28,19; 33,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,44; 31,5</t>
+          <t>26,32; 31,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,51; 34,03</t>
+          <t>28,45; 33,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,41; 49,19</t>
+          <t>33,82; 50,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,1; 39,06</t>
+          <t>33,03; 38,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,03; 32,02</t>
+          <t>27,14; 31,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,38; 34,16</t>
+          <t>29,27; 34,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,16; 43,83</t>
+          <t>34,32; 43,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,31; 35,36</t>
+          <t>31,11; 35,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,4; 30,78</t>
+          <t>27,18; 30,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,6; 33,29</t>
+          <t>29,6; 33,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,5; 45,55</t>
+          <t>35,11; 45,57</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,16; 35,98</t>
+          <t>28,88; 36,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,78; 32,7</t>
+          <t>25,86; 33,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,67; 33,43</t>
+          <t>27,19; 34,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,27; 37,12</t>
+          <t>30,12; 37,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,41; 38,35</t>
+          <t>30,4; 37,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,43; 37,47</t>
+          <t>28,99; 37,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,96; 34,73</t>
+          <t>27,8; 34,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,63; 42,96</t>
+          <t>35,04; 42,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,69; 35,96</t>
+          <t>30,76; 36,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,51; 33,92</t>
+          <t>28,43; 33,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,44; 33,17</t>
+          <t>28,5; 33,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,84; 39,0</t>
+          <t>33,35; 38,79</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,16; 37,11</t>
+          <t>30,27; 36,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,38; 31,43</t>
+          <t>25,69; 31,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,68; 35,55</t>
+          <t>28,47; 36,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,18; 37,63</t>
+          <t>29,09; 37,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,33; 37,34</t>
+          <t>29,91; 37,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,41; 33,49</t>
+          <t>26,28; 33,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,9; 36,43</t>
+          <t>28,95; 36,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,32; 43,49</t>
+          <t>31,32; 43,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,03; 36,04</t>
+          <t>31,31; 36,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,62; 30,98</t>
+          <t>26,69; 31,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,7; 34,67</t>
+          <t>29,43; 34,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,78; 39,68</t>
+          <t>31,9; 39,82</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,72; 34,91</t>
+          <t>26,91; 34,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,0; 33,19</t>
+          <t>25,42; 33,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,53; 31,96</t>
+          <t>24,61; 32,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30,14; 38,38</t>
+          <t>30,32; 38,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,77; 38,67</t>
+          <t>29,61; 38,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,28; 38,85</t>
+          <t>28,38; 38,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,88; 35,91</t>
+          <t>28,11; 35,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,6; 48,23</t>
+          <t>37,24; 48,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,56; 35,29</t>
+          <t>29,31; 35,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,1; 34,78</t>
+          <t>28,27; 34,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,42; 32,86</t>
+          <t>27,32; 33,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,12; 42,33</t>
+          <t>34,91; 42,75</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,08; 36,32</t>
+          <t>29,03; 36,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,11; 36,25</t>
+          <t>28,26; 36,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,08; 36,26</t>
+          <t>28,73; 35,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,43; 35,21</t>
+          <t>28,66; 35,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,37; 41,92</t>
+          <t>33,19; 42,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,8; 38,37</t>
+          <t>28,88; 38,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,66; 37,47</t>
+          <t>29,26; 37,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,02; 37,09</t>
+          <t>28,99; 37,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,52; 38,17</t>
+          <t>32,4; 37,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,05; 36,15</t>
+          <t>29,85; 36,06</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30,21; 35,67</t>
+          <t>30,04; 35,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,88; 35,21</t>
+          <t>29,96; 35,18</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,86; 33,77</t>
+          <t>28,76; 33,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,48; 33,95</t>
+          <t>28,31; 33,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,5; 32,12</t>
+          <t>27,42; 31,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,2; 39,46</t>
+          <t>33,27; 39,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,92; 35,68</t>
+          <t>29,53; 35,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,76; 32,97</t>
+          <t>27,81; 32,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,0; 31,8</t>
+          <t>26,98; 31,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,84; 45,85</t>
+          <t>38,11; 46,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,95; 33,83</t>
+          <t>30,06; 33,92</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,83; 32,9</t>
+          <t>28,7; 32,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,84; 31,23</t>
+          <t>27,77; 31,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,65; 42,09</t>
+          <t>36,64; 42,15</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>29,87; 34,09</t>
+          <t>29,96; 33,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,15; 32,2</t>
+          <t>28,17; 32,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,79; 30,81</t>
+          <t>26,95; 30,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,08; 37,42</t>
+          <t>33,02; 37,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,18; 34,74</t>
+          <t>30,09; 34,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,74; 33,14</t>
+          <t>28,62; 32,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,68; 32,27</t>
+          <t>27,67; 32,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,28; 40,83</t>
+          <t>35,45; 40,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,68; 33,61</t>
+          <t>30,64; 33,7</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28,93; 31,8</t>
+          <t>29,11; 32,02</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27,85; 30,79</t>
+          <t>27,83; 30,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>34,98; 38,77</t>
+          <t>35,04; 38,49</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30,74; 32,8</t>
+          <t>30,67; 32,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28,72; 30,82</t>
+          <t>28,74; 30,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,07; 31,1</t>
+          <t>29,11; 31,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33,25; 39,0</t>
+          <t>33,3; 38,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,83; 35,19</t>
+          <t>32,76; 35,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,67; 32,01</t>
+          <t>29,68; 32,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,94; 32,09</t>
+          <t>29,84; 31,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36,38; 39,59</t>
+          <t>36,28; 39,49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32,11; 33,67</t>
+          <t>32,02; 33,58</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29,54; 31,01</t>
+          <t>29,51; 31,06</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29,82; 31,29</t>
+          <t>29,76; 31,2</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>35,32; 38,26</t>
+          <t>35,36; 38,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Provincia-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35,06</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28,93</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30,9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31,02</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>30,43</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>29,04</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>30,23</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27,98</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>35,06</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,93</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,9</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30,32</t>
+          <t>29,68</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>30,39</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,74; 34,14</t>
+          <t>30,81; 40,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,97; 33,08</t>
+          <t>25,61; 33,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,98; 33,99</t>
+          <t>26,9; 35,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,69; 31,82</t>
+          <t>26,95; 35,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,64; 40,36</t>
+          <t>26,8; 34,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,56; 32,9</t>
+          <t>25,76; 32,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,7; 35,92</t>
+          <t>26,94; 34,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,75; 34,07</t>
+          <t>27,03; 33,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,68; 35,91</t>
+          <t>29,98; 35,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,68; 31,79</t>
+          <t>26,58; 31,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,94; 33,88</t>
+          <t>27,88; 33,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,23; 31,92</t>
+          <t>27,97; 33,06</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35,88</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29,34</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>31,66</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38,86</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>30,57</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>28,69</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>31,03</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>40,37</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>35,88</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>29,34</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>31,66</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38,18</t>
+          <t>35,8</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,28</t>
+          <t>37,43</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,19; 33,44</t>
+          <t>32,87; 38,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,32; 31,62</t>
+          <t>26,77; 31,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,45; 33,72</t>
+          <t>29,24; 34,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,82; 50,28</t>
+          <t>34,64; 44,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,03; 38,69</t>
+          <t>28,16; 33,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,14; 31,95</t>
+          <t>26,05; 31,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,27; 34,2</t>
+          <t>28,67; 34,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,32; 43,88</t>
+          <t>32,81; 39,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,11; 35,29</t>
+          <t>31,4; 35,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,18; 30,76</t>
+          <t>27,4; 31,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,6; 33,3</t>
+          <t>29,42; 33,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,11; 45,57</t>
+          <t>34,72; 40,65</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33,92</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33,1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>31,1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>39,15</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>32,81</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>28,98</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>30,26</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33,46</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>33,92</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>33,1</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31,1</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,77</t>
+          <t>33,83</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,25</t>
+          <t>36,51</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,88; 36,43</t>
+          <t>30,31; 37,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,86; 33,21</t>
+          <t>29,24; 37,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,19; 34,0</t>
+          <t>28,01; 34,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,12; 37,18</t>
+          <t>35,19; 43,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,4; 37,75</t>
+          <t>29,48; 36,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,99; 37,54</t>
+          <t>25,74; 33,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,8; 34,76</t>
+          <t>26,76; 33,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,04; 42,94</t>
+          <t>30,56; 37,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,76; 36,01</t>
+          <t>30,76; 36,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,43; 33,86</t>
+          <t>28,75; 33,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,5; 33,31</t>
+          <t>28,24; 33,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,35; 38,79</t>
+          <t>33,7; 39,01</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33,71</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29,49</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32,55</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37,24</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>33,56</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>28,42</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>31,88</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32,96</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>33,71</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,49</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,55</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,08</t>
+          <t>34,04</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,23</t>
+          <t>35,74</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,27; 36,91</t>
+          <t>30,18; 37,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,69; 31,84</t>
+          <t>26,03; 33,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,47; 36,04</t>
+          <t>29,3; 36,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,09; 37,65</t>
+          <t>31,66; 43,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,91; 37,22</t>
+          <t>30,37; 37,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,28; 33,04</t>
+          <t>25,61; 31,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,95; 36,62</t>
+          <t>28,54; 35,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,32; 43,25</t>
+          <t>29,94; 38,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,31; 36,11</t>
+          <t>31,23; 36,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,69; 31,5</t>
+          <t>26,77; 31,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,43; 34,75</t>
+          <t>29,54; 35,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,9; 39,82</t>
+          <t>32,11; 39,96</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33,72</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33,08</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>31,85</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>42,94</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>30,64</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>29,15</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>28,09</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>34,05</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>33,72</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>33,08</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>31,85</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41,98</t>
+          <t>34,24</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38,34</t>
+          <t>38,82</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,91; 34,86</t>
+          <t>29,42; 38,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,42; 33,59</t>
+          <t>28,52; 38,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,61; 32,0</t>
+          <t>28,07; 36,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30,32; 38,35</t>
+          <t>38,4; 49,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,61; 38,19</t>
+          <t>26,83; 34,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,38; 38,51</t>
+          <t>24,99; 33,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,11; 35,97</t>
+          <t>24,29; 32,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,24; 48,32</t>
+          <t>30,76; 39,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,31; 35,16</t>
+          <t>29,43; 35,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,27; 34,77</t>
+          <t>28,23; 34,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,32; 33,03</t>
+          <t>27,53; 32,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,91; 42,75</t>
+          <t>35,88; 42,49</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37,58</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>33,37</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33,14</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34,01</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>32,64</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>32,1</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>32,22</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31,96</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>37,58</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>33,37</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>33,14</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>32,81</t>
+          <t>33,0</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>32,42</t>
+          <t>33,52</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,03; 36,87</t>
+          <t>33,55; 42,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,26; 36,27</t>
+          <t>29,06; 38,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,73; 35,91</t>
+          <t>29,65; 37,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,66; 35,29</t>
+          <t>30,25; 38,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,19; 42,07</t>
+          <t>28,91; 36,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,88; 38,28</t>
+          <t>27,85; 35,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,26; 37,55</t>
+          <t>28,76; 35,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,99; 37,44</t>
+          <t>29,63; 36,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,4; 37,93</t>
+          <t>32,27; 38,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,85; 36,06</t>
+          <t>29,93; 35,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30,04; 35,61</t>
+          <t>30,08; 35,46</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,96; 35,18</t>
+          <t>31,02; 36,31</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>32,49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30,22</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>29,27</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>41,69</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>31,17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>30,98</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>29,61</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35,99</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>32,49</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30,22</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>29,27</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>41,46</t>
+          <t>36,85</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,02</t>
+          <t>39,46</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,76; 33,81</t>
+          <t>29,81; 35,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,31; 33,86</t>
+          <t>27,59; 33,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,42; 31,96</t>
+          <t>26,91; 31,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,27; 39,08</t>
+          <t>38,54; 47,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,53; 35,61</t>
+          <t>28,75; 33,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,81; 32,94</t>
+          <t>28,33; 33,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,98; 31,65</t>
+          <t>27,58; 31,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,11; 46,38</t>
+          <t>34,01; 39,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,06; 33,92</t>
+          <t>29,94; 33,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,7; 32,36</t>
+          <t>28,47; 32,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,77; 31,07</t>
+          <t>27,87; 31,08</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,64; 42,15</t>
+          <t>37,0; 42,41</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>32,32</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30,71</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>29,79</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>38,95</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>31,81</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>30,1</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>28,72</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>35,17</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>32,32</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>30,71</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>29,79</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38,08</t>
+          <t>36,04</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36,73</t>
+          <t>37,57</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>29,96; 33,8</t>
+          <t>30,11; 34,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,17; 32,2</t>
+          <t>28,54; 32,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,95; 30,74</t>
+          <t>27,6; 31,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,02; 37,34</t>
+          <t>36,52; 41,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,09; 34,72</t>
+          <t>29,73; 33,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,62; 32,78</t>
+          <t>28,04; 32,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,67; 32,04</t>
+          <t>26,9; 30,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,45; 40,87</t>
+          <t>33,66; 38,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,64; 33,7</t>
+          <t>30,65; 33,65</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29,11; 32,02</t>
+          <t>28,93; 31,83</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27,83; 30,82</t>
+          <t>27,77; 30,78</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,04; 38,49</t>
+          <t>35,99; 39,43</t>
         </is>
       </c>
     </row>
@@ -1768,42 +1768,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>33,98</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>30,75</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>30,89</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>38,48</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>31,68</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>29,79</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>30,09</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>34,89</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>33,98</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>30,75</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>30,89</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>37,73</t>
+          <t>34,84</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36,41</t>
+          <t>36,76</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30,67; 32,74</t>
+          <t>32,79; 35,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28,74; 30,97</t>
+          <t>29,52; 31,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,11; 31,11</t>
+          <t>29,86; 31,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33,3; 38,77</t>
+          <t>36,9; 40,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,76; 35,15</t>
+          <t>30,58; 32,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,68; 32,02</t>
+          <t>28,73; 30,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,84; 31,96</t>
+          <t>29,08; 31,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36,28; 39,49</t>
+          <t>33,58; 36,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32,02; 33,58</t>
+          <t>32,09; 33,71</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29,51; 31,06</t>
+          <t>29,51; 31,15</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29,76; 31,2</t>
+          <t>29,8; 31,25</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>35,36; 38,05</t>
+          <t>35,74; 37,88</t>
         </is>
       </c>
     </row>
